--- a/artfynd/A 25012-2023 artfynd.xlsx
+++ b/artfynd/A 25012-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,6 +913,229 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134579141</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rövarkulorna, Rövarkulorna, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>528935</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6585005</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fellingsbro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Såg ett blommande ex från cykel. Norra vägrenen.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134579147</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102637</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rövarkulorna, Rövarkulorna, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>528899</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6585018</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fellingsbro</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt i vägren.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25012-2023 artfynd.xlsx
+++ b/artfynd/A 25012-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126988137</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126988094</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134579141</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,8 +1155,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134579147</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>